--- a/new-info39/web.xlsx
+++ b/new-info39/web.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>domain</t>
   </si>
@@ -44,28 +44,22 @@
     <t>date</t>
   </si>
   <si>
-    <t>read.walrussea.com</t>
-  </si>
-  <si>
-    <t>#0c567d</t>
-  </si>
-  <si>
-    <t>sec.walrussea.com</t>
-  </si>
-  <si>
-    <t>#01847f</t>
-  </si>
-  <si>
-    <t>read.seacalmy.com</t>
-  </si>
-  <si>
-    <t>#ed9874</t>
-  </si>
-  <si>
-    <t>sec.seacalmy.com</t>
-  </si>
-  <si>
-    <t>#425066</t>
+    <t>aeolipile.cloud</t>
+  </si>
+  <si>
+    <t>#549688</t>
+  </si>
+  <si>
+    <t>futhark.cloud</t>
+  </si>
+  <si>
+    <t>#82f0f9</t>
+  </si>
+  <si>
+    <t>mipmap.site</t>
+  </si>
+  <si>
+    <t>#ffd7ed</t>
   </si>
   <si>
     <t>color1</t>
@@ -77,43 +71,40 @@
     <t>json</t>
   </si>
   <si>
-    <t>play.fellblade.com</t>
-  </si>
-  <si>
-    <t>#00000e</t>
-  </si>
-  <si>
-    <t>sec.fellblade.com</t>
+    <t>play.sepulchre.cloud</t>
+  </si>
+  <si>
+    <t>#e07563</t>
+  </si>
+  <si>
+    <t>sec.sepulchre.cloud</t>
+  </si>
+  <si>
+    <t>#41bbcb</t>
+  </si>
+  <si>
+    <t>play.kaleidos.fun</t>
+  </si>
+  <si>
+    <t>#f53d93</t>
+  </si>
+  <si>
+    <t>sec.kaleidos.fun</t>
+  </si>
+  <si>
+    <t>#ff978a</t>
+  </si>
+  <si>
+    <t>play.fervid.site</t>
+  </si>
+  <si>
+    <t>#6ae966</t>
+  </si>
+  <si>
+    <t>sec.fervid.site</t>
   </si>
   <si>
     <t>#a515f9</t>
-  </si>
-  <si>
-    <t>play.gloomward.cloud</t>
-  </si>
-  <si>
-    <t>#6ae966</t>
-  </si>
-  <si>
-    <t>sec.gloomward.cloud</t>
-  </si>
-  <si>
-    <t>#ff978a</t>
-  </si>
-  <si>
-    <t>play.kaleidos.fun</t>
-  </si>
-  <si>
-    <t>#f53d93</t>
-  </si>
-  <si>
-    <t>sec.kaleidos.fun</t>
-  </si>
-  <si>
-    <t>play.fervid.site</t>
-  </si>
-  <si>
-    <t>sec.fervid.site</t>
   </si>
   <si>
     <t>日期</t>
@@ -151,7 +142,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -199,22 +190,7 @@
     <font>
       <u/>
       <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFCE9178"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -235,6 +211,14 @@
     <font>
       <u/>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
       <color rgb="FF2972F4"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -399,7 +383,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,31 +428,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00000E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0C567D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF01847F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9874"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF425066"/>
+        <fgColor rgb="FFE07563"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41BBCB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF549688"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1660AB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82F0F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B313F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD7ED"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -768,85 +764,79 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -855,10 +845,10 @@
     <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -867,10 +857,10 @@
     <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -879,10 +869,10 @@
     <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -891,10 +881,10 @@
     <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -903,17 +893,23 @@
     <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -941,49 +937,46 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1396,27 +1389,27 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="19"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="19"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="15" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="21" t="s">
@@ -1426,176 +1419,169 @@
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>11</v>
-      </c>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="D21" s="25"/>
+      <c r="D21" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1"/>
     <hyperlink ref="F17" r:id="rId2"/>
-    <hyperlink ref="A2" r:id="rId3" display="read.walrussea.com" tooltip="http://read.walrussea.com"/>
-    <hyperlink ref="A3" r:id="rId4" display="sec.walrussea.com" tooltip="http://sec.walrussea.com"/>
-    <hyperlink ref="A4" r:id="rId5" display="read.seacalmy.com" tooltip="http://seacalmy.com"/>
-    <hyperlink ref="A5" r:id="rId5" display="sec.seacalmy.com" tooltip="http://seacalmy.com"/>
+    <hyperlink ref="A5" r:id="rId3" tooltip="http://seacalmy.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1616,91 +1602,75 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="11" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12">
         <v>2</v>
       </c>
-      <c r="E3" s="4">
-        <v>7</v>
+      <c r="E3" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>3</v>
-      </c>
-      <c r="E4" s="4">
-        <v>7</v>
-      </c>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
-        <v>4</v>
-      </c>
-      <c r="E5" s="4">
-        <v>7</v>
-      </c>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4"/>
@@ -1717,25 +1687,25 @@
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1745,8 +1715,6 @@
     <hyperlink ref="A11" r:id="rId4"/>
     <hyperlink ref="A6" r:id="rId5" tooltip="http://gravecaller.com"/>
     <hyperlink ref="A7" r:id="rId5" tooltip="http://gravecaller.com"/>
-    <hyperlink ref="A2" r:id="rId6" display="play.fellblade.com" tooltip="https://play.fellblade.com"/>
-    <hyperlink ref="A3" r:id="rId7" display="sec.fellblade.com" tooltip="https://sec.fellblade.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1767,24 +1735,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7">
@@ -1797,10 +1765,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="7">
@@ -1813,10 +1781,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="7">
@@ -1829,10 +1797,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="7">
@@ -1881,28 +1849,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8">
